--- a/tests/fixtures/formula_storage/kinds.xlsx
+++ b/tests/fixtures/formula_storage/kinds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\formula_storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{028F8923-7EDF-4F49-9B58-FEDF1802A6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A679C8B8-CC79-47E0-BD5B-F868907A54C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="7200" windowHeight="4425" xr2:uid="{EBEDA356-CC7B-4B74-9359-66D9BFB0E310}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4425" xr2:uid="{FEEA45A8-3315-460D-85CD-C0A5D591BF05}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B2FE45-5D1F-499B-930A-E2FED521E169}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCCA4A1A-E044-42F6-A29B-755B5E304058}">
   <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/tests/fixtures/formula_storage/kinds.xlsx
+++ b/tests/fixtures/formula_storage/kinds.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\formula_storage\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{A679C8B8-CC79-47E0-BD5B-F868907A54C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4425" xr2:uid="{FEEA45A8-3315-460D-85CD-C0A5D591BF05}"/>
